--- a/交付物/01_教材版本总表/湖北省咸宁市2025-2026学年中小学教材版本总表.xlsx
+++ b/交付物/01_教材版本总表/湖北省咸宁市2025-2026学年中小学教材版本总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="官方平台与链接" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'教材版本总表'!$A$3:$J$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'教材版本总表'!$A$3:$J$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4404,19 +4404,1423 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="46" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>人教版（统编版）必修上册</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>人教版（统编版）必修下册</t>
+        </is>
+      </c>
+      <c r="G75" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I75" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J75" s="22" t="inlineStr">
+        <is>
+          <t>统编版高中语文必修；共8单元，含整本书阅读《乡土中国》《红楼梦》</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>人教版（统编版）选择性必修上册</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>人教版（统编版）选择性必修中册、下册</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J76" s="17" t="inlineStr">
+        <is>
+          <t>选择性必修3册，以专题研习任务群组织教学</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>人教版（统编版）高考总复习</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>人教版（统编版）高考总复习</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I77" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>依据新高考评价体系与课程标准进行总复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>人教A版 必修第一册</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>人教A版 必修第二册</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>集合与逻辑、函数、三角函数、平面向量、立体几何、统计概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>人教A版 选择性必修第一册</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>人教A版 选择性必修第二册、第三册</t>
+        </is>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I79" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J79" s="22" t="inlineStr">
+        <is>
+          <t>空间向量与立体几何、直线与圆、圆锥曲线、数列、导数、计数原理、随机变量</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>人教A版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>人教A版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>函数与导数、三角数列、解析几何、概率统计等主干专题复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr">
+        <is>
+          <t>人教版 必修第一册</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>人教版 必修第二册、第三册</t>
+        </is>
+      </c>
+      <c r="G81" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I81" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J81" s="22" t="inlineStr">
+        <is>
+          <t>人教版高中英语必修3册，主题语境引领</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修第一册</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修第二册、第三册、第四册</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>选择性必修4册，强化语篇与语言运用</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E83" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G83" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I83" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J83" s="22" t="inlineStr">
+        <is>
+          <t>阅读理解、完形填空、语法填空、七选五与书面表达专项训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>人教版 必修第一册</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>人教版 必修第二册</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>运动与力、牛顿运动定律、曲线运动、万有引力与机械能</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>人教版 必修第三册</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修第一册、第二册</t>
+        </is>
+      </c>
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I85" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J85" s="22" t="inlineStr">
+        <is>
+          <t>静电场、恒定电流、磁场、电磁感应、交变电流、动量与机械振动</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>力学、电磁学主干与热学、光学、近代物理等选修模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>人教版 必修第一册</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>人教版 必修第二册</t>
+        </is>
+      </c>
+      <c r="G87" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I87" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J87" s="22" t="inlineStr">
+        <is>
+          <t>物质及其变化、离子反应、铁及金属材料、无机非金属材料、化学反应与能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修1 化学反应原理</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修2、3</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>反应热、速率与平衡、水溶液离子平衡、电化学、物质结构与有机化学基础</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I89" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J89" s="22" t="inlineStr">
+        <is>
+          <t>基本概念与理论、元素化学、有机化学、实验化学与化工流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>人教版 必修1 分子与细胞</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>人教版 必修2 遗传与进化</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>细胞的结构与功能、物质运输、能量供应与利用、遗传的基本规律与进化</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修1 稳态与调节</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>人教版 选择性必修2、3</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I91" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J91" s="22" t="inlineStr">
+        <is>
+          <t>内环境与稳态、神经体液免疫调节、生物与环境、生物技术与工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>人教版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>分子与细胞、遗传与进化、稳态与调节、生物与环境综合复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>思想政治</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr">
+        <is>
+          <t>统编版 必修1 中国特色社会主义</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>统编版 必修2 经济与社会、必修3 政治与法治</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I93" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J93" s="22" t="inlineStr">
+        <is>
+          <t>中国特色社会主义、经济与社会、政治与法治、哲学与文化</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>思想政治</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>统编版 选择性必修1 当代国际政治与经济</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>统编版 选择性必修2 法律与生活、选择性必修3 逻辑与思维</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t>国际政治与经济、法律与生活、逻辑与思维</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>思想政治</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>统编版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>统编版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I95" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J95" s="22" t="inlineStr">
+        <is>
+          <t>辩证唯物主义、经济政治法治、文化生活等模块综合复习与时政分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>统编版 中外历史纲要（上）</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>统编版 中外历史纲要（下）</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t>纲要上为中国通史，纲要下为世界通史，按通史体例编排</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>统编版 选择性必修1 国家制度与社会治理</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>统编版 选择性必修2 经济与社会生活、选择性必修3 文化交流与传播</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I97" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J97" s="22" t="inlineStr">
+        <is>
+          <t>国家制度与社会治理、经济与社会生活、文化交流与传播</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>统编版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>统编版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>人民教育出版社</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
+        <is>
+          <t>中国史与世界史专题整合、史料实证与历史解释能力训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 必修第一册</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 必修第二册</t>
+        </is>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>2019版</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社</t>
+        </is>
+      </c>
+      <c r="I99" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J99" s="22" t="inlineStr">
+        <is>
+          <t>咸宁选用中图版；必修1自然地理，必修2人文地理</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 选择性必修1 自然地理基础</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 选择性必修2、3</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>2020版</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>中国地图出版社</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t>自然地理基础、区域发展、资源环境与国家安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 高考总复习</t>
+        </is>
+      </c>
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社版 高考总复习</t>
+        </is>
+      </c>
+      <c r="G101" s="20" t="inlineStr">
+        <is>
+          <t>全国卷</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>中国地图出版社</t>
+        </is>
+      </c>
+      <c r="I101" s="23" t="inlineStr">
+        <is>
+          <t>https://basic.smartedu.cn/tchMaterial</t>
+        </is>
+      </c>
+      <c r="J101" s="22" t="inlineStr">
+        <is>
+          <t>自然地理与人文地理主干、区域可持续发展与地理实践力训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="46" customHeight="1">
+      <c r="A103" s="24" t="inlineStr">
         <is>
           <t>说明：① 咸宁市小学语文/数学/道德与法治、初中语文/数学/历史/道德与法治/生物/地理/化学均为人教版（统编版）；初中英语为仁爱版（科普版）；初中物理为北师大版（部分区县人教版）；小学科学为人教·鄂教版。② 「版次」反映新教材替换进度，部分年级2026秋起完成统编替换。③ 官方电子教材均可通过国家中小学智慧教育平台或湖北省数字教材平台免费浏览/下载。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J74"/>
+  <autoFilter ref="A3:J101"/>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A103:J103"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
@@ -4490,6 +5894,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
